--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/Мелитополь/дв 24,09,26 млрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/Мелитополь/дв 24,09,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\Мелитополь\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\Создание расчетов\ПОКОМ_КИ_UK_Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB423333-22C1-48CE-8D5C-7F98D17CCF9A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106C0D14-6C8B-48D2-A5C5-B7161D3B6215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,20 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AM$128</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="301">
   <si>
     <t>дн</t>
   </si>
@@ -932,6 +924,9 @@
   <si>
     <t>БОНУС_615  Гречка по-купечески с говядиной и овощами 0,325кг ТМ Стародворье  ПОКОМ</t>
   </si>
+  <si>
+    <t>29,09,доз</t>
+  </si>
 </sst>
 </file>
 
@@ -1696,7 +1691,7 @@
         <v>32</v>
       </c>
       <c r="Y4" s="18" t="s">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
